--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -484,11 +855,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,32 +917,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>L. Barrett</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -632,16 +1037,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.3</v>
+        <v>74.8</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.6</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1056,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112.8</v>
+        <v>113.5</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1075,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98.40000000000001</v>
+        <v>109.9</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>-12</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1094,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.4</v>
+        <v>3.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +1116,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.2</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="7">
@@ -727,13 +1132,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -749,7 +1154,7 @@
         <v>0.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -765,16 +1170,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -889,7 +1294,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -980,6 +1385,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Know the first reference: J. Slater is a paint finisher, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -994,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1016,24 +1433,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from L. Muhammad and A. Dziewa; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are L. Barrett and J. Slater; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from G. Crandall and L. Muhammad; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1045,17 +1462,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially L. Muhammad and J. Slater; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially L. Muhammad, J. Slater, and L. Barrett; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Second-chance threat; the first stop is not enough against this team.</t>
         </is>
@@ -1072,23 +1501,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1103,18 +1783,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1202,36 +1882,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1248,36 +1928,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1294,32 +1974,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1335,38 +2015,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>29.4%</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,23 +2074,23 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -1424,19 +2114,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -1460,7 +2150,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1472,7 +2162,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -1492,42 +2182,34 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SLB_L._MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1536,23 +2218,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -1564,12 +2246,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1580,23 +2262,243 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SLB_J._SLATER</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SLB_A._BROUSSARD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M15" t="n">
         <v>1.6</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,31 +515,31 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -567,41 +567,41 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
@@ -619,21 +619,21 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -660,47 +660,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,47 +712,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -764,52 +764,104 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>3.5</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3.3</t>
         </is>
       </c>
     </row>
@@ -824,24 +876,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>J. Slater | L. Barrett</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G. Crandall | J. Slater</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G. Crandall | L. Barrett</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.1</v>
       </c>
     </row>
   </sheetData>
@@ -855,12 +1023,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -951,32 +1119,66 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>lineups</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (12.1 min)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (19.9 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -1037,16 +1239,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.8</v>
+        <v>78.2</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="3">
@@ -1056,16 +1258,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113.5</v>
+        <v>111.5</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4">
@@ -1075,16 +1277,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109.9</v>
+        <v>98.7</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="5">
@@ -1094,16 +1296,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6</v>
+        <v>12.8</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="6">
@@ -1113,16 +1315,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="7">
@@ -1132,13 +1334,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1157,7 +1359,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1170,16 +1372,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
@@ -1195,10 +1397,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1258,7 +1460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1562,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1450,19 +1652,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from G. Crandall and L. Muhammad; contest, but do not over-help into secondary advantages.</t>
+          <t>Priority closeouts start with A. Broussard, G. Crandall, and J. Slater; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Some perimeter volume comes from J. Slater and G. Crandall; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1474,19 +1676,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially L. Muhammad, J. Slater, and L. Barrett; force them away from preferred areas.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially L. Muhammad, J. Slater, and A. Broussard; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: J. Slater | L. Barrett and G. Crandall | J. Slater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose A. Broussard and G. Crandall in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1568,27 +1806,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="D2" t="n">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1842,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="D3" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1640,17 +1878,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1667,67 +1905,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.3</v>
+        <v>25.9</v>
       </c>
       <c r="D5" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>25.3</v>
       </c>
       <c r="D6" t="n">
-        <v>13.5</v>
+        <v>10.7</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1739,36 +1977,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>19.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>11.7</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1783,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1877,37 +2115,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1923,41 +2161,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1969,37 +2207,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2020,32 +2258,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2061,110 +2299,140 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>36</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>26.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>35</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>25.7%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB_L._MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>36</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>22.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2182,23 +2450,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -2218,42 +2486,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>27.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SLB_L._MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -2262,42 +2522,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SLB_J._SLATER</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>J. Slater</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2306,42 +2558,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SLB_L._BARRETT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>L. Barrett</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2350,7 +2594,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2358,15 +2602,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2622,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2394,23 +2638,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2666,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2442,19 +2686,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2710,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2486,19 +2730,195 @@
         </is>
       </c>
       <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>36.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SLB_L._BARRETT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SLB_G._CRANDALL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SLB_A._DZIEWA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>38.5%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SLB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,21 +515,21 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,88 +567,88 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -660,47 +660,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,52 +712,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -775,26 +775,26 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -827,31 +827,31 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -861,7 +861,59 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLB_E._FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E. Francisco</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -876,12 +928,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -942,16 +994,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59.6</v>
+        <v>76.8</v>
       </c>
       <c r="E2" t="n">
-        <v>89.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="F2" t="n">
-        <v>69.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G2" t="n">
-        <v>20.8</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="3">
@@ -967,26 +1019,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater</t>
+          <t>A. Broussard | J. Slater</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58.2</v>
+        <v>64.2</v>
       </c>
       <c r="E3" t="n">
-        <v>93.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F3" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="G3" t="n">
-        <v>23.4</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -996,20 +1048,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G. Crandall | L. Barrett</t>
+          <t>A. Broussard | A. Dziewa | L. Muhammad</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49.8</v>
+        <v>51.7</v>
       </c>
       <c r="E4" t="n">
-        <v>84.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>68.2</v>
+        <v>66.5</v>
       </c>
       <c r="G4" t="n">
-        <v>16.1</v>
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Broussard | A. Dziewa | L. Muhammad</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
@@ -1129,7 +1210,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (12.1 min)</t>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (18.7 min)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (19.9 net)</t>
+          <t>A. Broussard | A. Dziewa | J. Slater | L. Barrett | L. Muhammad (39.6 net)</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1244,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1239,16 +1320,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.2</v>
+        <v>79.8</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1258,16 +1339,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>111.5</v>
+        <v>110</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4">
@@ -1277,16 +1358,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.3</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1296,16 +1377,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.8</v>
+        <v>15.1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>13.1</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="6">
@@ -1315,16 +1396,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1340,7 +1421,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1353,7 +1434,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="n">
         <v>0.3</v>
@@ -1372,16 +1453,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -1391,13 +1472,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1472,7 +1553,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Below-average assist profile; more possessions end through direct creation than collective flow.</t>
+          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1589,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1757,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1769,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially L. Muhammad, J. Slater, and A. Broussard; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially J. Slater, L. Muhammad, and A. Broussard; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1781,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: J. Slater | L. Barrett and G. Crandall | J. Slater.</t>
+          <t>Recognize the main duo/trio combinations: J. Slater | L. Barrett and A. Broussard | J. Slater.</t>
         </is>
       </c>
     </row>
@@ -1806,27 +1887,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1923,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1869,31 +1950,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1905,62 +1986,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="D5" t="n">
-        <v>12.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1970,7 +2051,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1986,17 +2067,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2021,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2129,20 +2210,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
         <v>0.9</v>
@@ -2175,23 +2256,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2221,23 +2302,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2253,41 +2334,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SLB_J._SLATER</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Slater</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2304,36 +2385,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_J._SLATER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>J. Slater</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2350,36 +2431,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SLB_L._MUHAMMAD</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2396,36 +2477,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SLB_L._SILVA</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L. Silva</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2437,38 +2518,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>58</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24.1%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2490,19 +2581,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
     </row>
@@ -2522,23 +2613,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2649,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -2594,42 +2685,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SLB_L._MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2638,23 +2721,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -2686,19 +2769,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2793,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLB_A._BROUSSARD</t>
+          <t>SLB_L._MUHAMMAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>L. Muhammad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2726,23 +2809,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2837,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SLB_L._BARRETT</t>
+          <t>SLB_A._BROUSSARD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L. Barrett</t>
+          <t>A. Broussard</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2770,23 +2853,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SLB_G._CRANDALL</t>
+          <t>SLB_L._BARRETT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
+          <t>L. Barrett</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2814,23 +2897,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2925,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SLB_A._DZIEWA</t>
+          <t>SLB_G._CRANDALL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Dziewa</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2858,23 +2941,23 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2969,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SLB_D._RELVAO</t>
+          <t>SLB_A._DZIEWA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D. Relvao</t>
+          <t>A. Dziewa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2906,19 +2989,107 @@
         </is>
       </c>
       <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SLB_L._SILVA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>L. Silva</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SLB_D._RELVAO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="M22" t="n">
         <v>1.6</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>38.5%</t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
